--- a/histograms/histogram_Log_rate.xlsx
+++ b/histograms/histogram_Log_rate.xlsx
@@ -442,162 +442,162 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-8.963959854043548</v>
+        <v>-4.191100649182597</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-7.640167930254945</v>
+        <v>-3.362961575571608</v>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-6.316376006466343</v>
+        <v>-2.534822501960621</v>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-4.992584082677741</v>
+        <v>-1.706683428349633</v>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-3.668792158889139</v>
+        <v>-0.8785443547386447</v>
       </c>
       <c r="B6" t="n">
-        <v>164</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-2.345000235100536</v>
+        <v>-0.05040528112765674</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-1.021208311311934</v>
+        <v>0.7777337924833314</v>
       </c>
       <c r="B8" t="n">
-        <v>825</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.3025836124766679</v>
+        <v>1.60587286609432</v>
       </c>
       <c r="B9" t="n">
-        <v>1398</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1.626375536265271</v>
+        <v>2.434011939705307</v>
       </c>
       <c r="B10" t="n">
-        <v>2226</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2.950167460053873</v>
+        <v>3.262151013316295</v>
       </c>
       <c r="B11" t="n">
-        <v>3097</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4.273959383842475</v>
+        <v>4.090290086927284</v>
       </c>
       <c r="B12" t="n">
-        <v>3631</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5.597751307631078</v>
+        <v>4.918429160538271</v>
       </c>
       <c r="B13" t="n">
-        <v>3712</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.92154323141968</v>
+        <v>5.746568234149259</v>
       </c>
       <c r="B14" t="n">
-        <v>3355</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8.245335155208281</v>
+        <v>6.574707307760248</v>
       </c>
       <c r="B15" t="n">
-        <v>2698</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9.569127078996884</v>
+        <v>7.402846381371236</v>
       </c>
       <c r="B16" t="n">
-        <v>2021</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10.89291900278549</v>
+        <v>8.230985454982223</v>
       </c>
       <c r="B17" t="n">
-        <v>1391</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12.21671092657409</v>
+        <v>9.059124528593211</v>
       </c>
       <c r="B18" t="n">
-        <v>836</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13.54050285036269</v>
+        <v>9.887263602204198</v>
       </c>
       <c r="B19" t="n">
-        <v>422</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14.86429477415129</v>
+        <v>10.71540267581519</v>
       </c>
       <c r="B20" t="n">
-        <v>130</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16.18808669793989</v>
+        <v>11.54354174942618</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
